--- a/01_Input/00_CO Validation/Bosnia and Herzegovina - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Bosnia and Herzegovina - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27016"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="360" documentId="11_7A16C5C5EBEF1110EA3321A633CA6B1980AA3C4F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40877100-3938-4977-8482-7650F041252D}"/>
+  <xr:revisionPtr revIDLastSave="376" documentId="11_7A16C5C5EBEF1110EA3321A633CA6B1980AA3C4F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AED13005-3816-4820-B528-337156BC0FEF}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,6 +15,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="138">
   <si>
     <t>Project ID</t>
   </si>
@@ -111,9 +114,15 @@
     <t>Government Capacity-Building</t>
   </si>
   <si>
+    <t>Energy Efficiency</t>
+  </si>
+  <si>
     <t>Number of public builidings retrofitted</t>
   </si>
   <si>
+    <t>5 buildings</t>
+  </si>
+  <si>
     <t>Target met in 2022. Energy efficient retrofitting of additional 5 buildings in BIH</t>
   </si>
   <si>
@@ -123,48 +132,48 @@
     <t>http://open.undp.org/projects/00105415</t>
   </si>
   <si>
+    <t>Number of people who directly benefit from energy efficiency improvements in public infrastructure/buildings, including street lightening.</t>
+  </si>
+  <si>
+    <t>EE retrofit of public buidlings and public lightning sytems</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>Accelerating just energy transition</t>
+  </si>
+  <si>
+    <t>Green Deal</t>
+  </si>
+  <si>
+    <t>http://open.undp.org/projects/00131266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of residential households with improved EE </t>
+  </si>
+  <si>
+    <t>251 HH</t>
+  </si>
+  <si>
+    <t>Medium Enterprises</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of SMEs with improved EE </t>
+  </si>
+  <si>
+    <t>Green Economic Development Project – III Phase</t>
+  </si>
+  <si>
+    <t>http://open.undp.org/projects/00132013</t>
+  </si>
+  <si>
+    <t>40 buildings</t>
+  </si>
+  <si>
     <t>Other Energy Services</t>
   </si>
   <si>
-    <t>Number of people who directly benefit from energy efficiency improvements in public infrastructure/buildings, including street lightening.</t>
-  </si>
-  <si>
-    <t>EE retrofit of public buidlings and public lightning sytems</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>Accelerating just energy transition</t>
-  </si>
-  <si>
-    <t>Energy Efficiency</t>
-  </si>
-  <si>
-    <t>Green Deal</t>
-  </si>
-  <si>
-    <t>http://open.undp.org/projects/00131266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of residential households with improved EE </t>
-  </si>
-  <si>
-    <t>251 HH</t>
-  </si>
-  <si>
-    <t>Medium Enterprises</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of SMEs with improved EE </t>
-  </si>
-  <si>
-    <t>Green Economic Development Project – III Phase</t>
-  </si>
-  <si>
-    <t>http://open.undp.org/projects/00132013</t>
-  </si>
-  <si>
     <t xml:space="preserve">Number of off-grid households in remote areas in BiH </t>
   </si>
   <si>
@@ -208,6 +217,9 @@
   </si>
   <si>
     <t>PIMS+</t>
+  </si>
+  <si>
+    <t>430 buildings</t>
   </si>
   <si>
     <t>(by the end of 2022 result was 100 public buildings)</t>
@@ -472,7 +484,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -524,6 +536,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -620,7 +638,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -694,6 +712,30 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -706,9 +748,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1093,25 +1132,25 @@
       <c r="B2" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="33" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="16">
         <v>29752153</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="20">
+      <c r="G2" s="35">
         <v>0</v>
       </c>
-      <c r="H2" s="20">
+      <c r="H2" s="35">
         <v>120</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="36" t="s">
         <v>22</v>
       </c>
       <c r="J2" s="15"/>
@@ -1135,24 +1174,25 @@
     <row r="3" spans="1:18" ht="50.25" customHeight="1">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="22" t="s">
+      <c r="C3" s="33"/>
+      <c r="E3" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="23">
+      <c r="F3" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="39">
         <v>0</v>
       </c>
-      <c r="H3" s="23">
-        <v>5</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>27</v>
+      <c r="H3" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="36" t="s">
+        <v>29</v>
       </c>
       <c r="J3" s="15"/>
       <c r="K3" s="15"/>
-      <c r="L3" s="38"/>
+      <c r="L3" s="40"/>
       <c r="M3" s="15"/>
       <c r="N3" s="15"/>
       <c r="O3" s="15"/>
@@ -1165,40 +1205,40 @@
         <v>105415</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>31</v>
       </c>
       <c r="D4" s="16">
         <v>18383776</v>
       </c>
-      <c r="E4" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="20">
+      <c r="E4" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="35">
         <v>567</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="35">
         <v>2698</v>
       </c>
-      <c r="I4" s="21" t="s">
-        <v>32</v>
+      <c r="I4" s="36" t="s">
+        <v>33</v>
       </c>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
-      <c r="L4" s="38"/>
+      <c r="L4" s="40"/>
       <c r="M4" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
@@ -1211,36 +1251,36 @@
       <c r="B5" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="41" t="s">
         <v>37</v>
       </c>
       <c r="D5" s="15">
         <v>614042</v>
       </c>
-      <c r="E5" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="22" t="s">
+      <c r="E5" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="15">
         <v>146</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="18"/>
+      <c r="I5" s="15"/>
       <c r="J5" s="15"/>
       <c r="K5" s="15"/>
-      <c r="L5" s="38"/>
+      <c r="L5" s="40"/>
       <c r="M5" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="P5" s="15"/>
       <c r="Q5" s="15"/>
@@ -1249,32 +1289,32 @@
     <row r="6" spans="1:18" ht="30.75">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
-      <c r="C6" s="24"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="15"/>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="15">
         <v>0</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="15">
         <v>15</v>
       </c>
-      <c r="I6" s="18"/>
+      <c r="I6" s="15"/>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
-      <c r="L6" s="38"/>
+      <c r="L6" s="40"/>
       <c r="M6" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="P6" s="15"/>
       <c r="Q6" s="15"/>
@@ -1287,36 +1327,36 @@
       <c r="B7" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="41" t="s">
         <v>43</v>
       </c>
       <c r="D7" s="15">
         <v>6294159</v>
       </c>
-      <c r="E7" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="22" t="s">
+      <c r="E7" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="18">
+      <c r="F7" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="15">
         <v>0</v>
       </c>
-      <c r="H7" s="18">
-        <v>40</v>
-      </c>
-      <c r="I7" s="18"/>
+      <c r="H7" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="15"/>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
-      <c r="L7" s="38"/>
+      <c r="L7" s="40"/>
       <c r="M7" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="P7" s="15"/>
       <c r="Q7" s="15"/>
@@ -1325,24 +1365,24 @@
     <row r="8" spans="1:18" ht="106.5">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
-      <c r="C8" s="24"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="15"/>
-      <c r="E8" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="18">
+      <c r="E8" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="15">
         <v>0</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="15">
         <v>49000</v>
       </c>
-      <c r="I8" s="18"/>
+      <c r="I8" s="15"/>
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
-      <c r="L8" s="38"/>
+      <c r="L8" s="40"/>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
       <c r="O8" s="15"/>
@@ -1353,24 +1393,24 @@
     <row r="9" spans="1:18" ht="45.75">
       <c r="A9" s="15"/>
       <c r="B9" s="15"/>
-      <c r="C9" s="24"/>
+      <c r="C9" s="41"/>
       <c r="D9" s="15"/>
-      <c r="E9" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="18">
+      <c r="E9" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="15">
         <v>0</v>
       </c>
-      <c r="H9" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="18"/>
+      <c r="H9" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="15"/>
       <c r="J9" s="15"/>
       <c r="K9" s="15"/>
-      <c r="L9" s="38"/>
+      <c r="L9" s="40"/>
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
       <c r="O9" s="15"/>
@@ -1383,47 +1423,47 @@
         <v>132014</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>49</v>
       </c>
       <c r="D10" s="15">
         <v>1771084</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="18">
+      <c r="F10" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="15">
         <v>0</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="15">
         <v>36</v>
       </c>
-      <c r="I10" s="22" t="s">
-        <v>49</v>
+      <c r="I10" s="38" t="s">
+        <v>51</v>
       </c>
       <c r="J10" s="15"/>
       <c r="K10" s="15"/>
-      <c r="L10" s="38"/>
+      <c r="L10" s="40"/>
       <c r="M10" s="15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N10" s="15" t="s">
         <v>23</v>
       </c>
       <c r="O10" s="15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="P10" s="15"/>
       <c r="Q10" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="45.75">
@@ -1431,36 +1471,36 @@
         <v>141105</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>55</v>
       </c>
       <c r="D11" s="15">
         <v>821580</v>
       </c>
-      <c r="E11" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" s="18">
+      <c r="E11" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="15">
         <v>0</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="15">
         <v>20</v>
       </c>
-      <c r="I11" s="22"/>
+      <c r="I11" s="38"/>
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
-      <c r="L11" s="38"/>
+      <c r="L11" s="40"/>
       <c r="M11" s="15"/>
       <c r="N11" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O11" s="15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="P11" s="15"/>
       <c r="Q11" s="15"/>
@@ -1469,24 +1509,24 @@
     <row r="12" spans="1:18">
       <c r="A12" s="15"/>
       <c r="B12" s="15"/>
-      <c r="C12" s="24"/>
+      <c r="C12" s="41"/>
       <c r="D12" s="15"/>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" s="18">
+      <c r="F12" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="15">
         <v>0</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="15">
         <v>20</v>
       </c>
-      <c r="I12" s="22"/>
+      <c r="I12" s="38"/>
       <c r="J12" s="15"/>
       <c r="K12" s="15"/>
-      <c r="L12" s="38"/>
+      <c r="L12" s="40"/>
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
       <c r="O12" s="15"/>
@@ -1499,38 +1539,40 @@
         <v>5882</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D13" s="15">
         <v>17346000</v>
       </c>
-      <c r="E13" s="18"/>
-      <c r="F13" s="22" t="s">
+      <c r="E13" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="G13" s="18">
+      <c r="F13" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="15">
         <v>0</v>
       </c>
-      <c r="H13" s="18">
-        <v>430</v>
-      </c>
-      <c r="I13" s="22" t="s">
-        <v>59</v>
+      <c r="H13" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" s="38" t="s">
+        <v>62</v>
       </c>
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
-      <c r="L13" s="38" t="s">
-        <v>60</v>
+      <c r="L13" s="40" t="s">
+        <v>63</v>
       </c>
       <c r="M13" s="15"/>
       <c r="N13" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O13" s="15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="P13" s="15"/>
       <c r="Q13" s="15"/>
@@ -1541,24 +1583,24 @@
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
-      <c r="E14" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="18">
+      <c r="E14" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="15">
         <v>0</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="15">
         <v>380754</v>
       </c>
-      <c r="I14" s="22" t="s">
-        <v>62</v>
+      <c r="I14" s="38" t="s">
+        <v>65</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
-      <c r="L14" s="38"/>
+      <c r="L14" s="40"/>
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
@@ -1567,27 +1609,27 @@
       <c r="R14" s="15"/>
     </row>
     <row r="15" spans="1:18" s="31" customFormat="1" ht="30.75">
-      <c r="A15" s="29"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15">
         <v>0</v>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="15">
         <v>4770</v>
       </c>
-      <c r="I15" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="29"/>
+      <c r="I15" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="15"/>
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
       <c r="P15" s="15"/>
@@ -1599,31 +1641,31 @@
         <v>5646</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D16" s="15">
         <v>2370000</v>
       </c>
-      <c r="E16" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16" s="18">
+      <c r="E16" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="15">
         <v>0</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="15">
         <v>67826</v>
       </c>
-      <c r="I16" s="22"/>
+      <c r="I16" s="38"/>
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
-      <c r="L16" s="38" t="s">
-        <v>60</v>
+      <c r="L16" s="40" t="s">
+        <v>63</v>
       </c>
       <c r="M16" s="15"/>
       <c r="N16" s="15" t="s">
@@ -1637,27 +1679,27 @@
       <c r="R16" s="15"/>
     </row>
     <row r="17" spans="1:18" s="31" customFormat="1" ht="45.75">
-      <c r="A17" s="29"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17" s="29">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="15">
         <v>0</v>
       </c>
-      <c r="H17" s="29">
+      <c r="H17" s="15">
         <v>360000</v>
       </c>
-      <c r="I17" s="30"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="39"/>
-      <c r="M17" s="29"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="15"/>
       <c r="N17" s="15" t="s">
         <v>23</v>
       </c>
@@ -1767,7 +1809,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="28" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="O1" s="28" t="s">
         <v>13</v>
@@ -1796,7 +1838,7 @@
         <v>19</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E2" s="18" t="s">
         <v>20</v>
@@ -1836,7 +1878,7 @@
       <c r="D3" s="16"/>
       <c r="E3" s="18"/>
       <c r="F3" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" s="23">
         <v>0</v>
@@ -1845,7 +1887,7 @@
         <v>5</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J3" s="15"/>
       <c r="K3" s="15"/>
@@ -1856,19 +1898,19 @@
         <v>105415</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="20">
         <v>567</v>
@@ -1877,16 +1919,16 @@
         <v>2698</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="L4" s="15"/>
       <c r="O4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P4" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="45.75">
@@ -1900,10 +1942,10 @@
         <v>37</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>38</v>
@@ -1919,10 +1961,10 @@
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
       <c r="O5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P5" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="30.75">
@@ -1958,13 +2000,13 @@
         <v>43</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G7" s="18">
         <v>0</v>
@@ -1977,10 +2019,10 @@
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
       <c r="O7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P7" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="106.5">
@@ -1989,10 +2031,10 @@
       <c r="C8" s="24"/>
       <c r="D8" s="15"/>
       <c r="E8" s="18" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8" s="18">
         <v>0</v>
@@ -2011,16 +2053,16 @@
       <c r="C9" s="24"/>
       <c r="D9" s="15"/>
       <c r="E9" s="18" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G9" s="18">
         <v>0</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I9" s="18"/>
       <c r="J9" s="15"/>
@@ -2032,19 +2074,19 @@
         <v>132014</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E10" s="18" t="s">
         <v>20</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G10" s="18">
         <v>0</v>
@@ -2053,7 +2095,7 @@
         <v>36</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J10" s="15"/>
       <c r="K10" s="15"/>
@@ -2062,13 +2104,13 @@
         <v>23</v>
       </c>
       <c r="P10" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="R10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="S10" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="45.75">
@@ -2076,19 +2118,19 @@
         <v>141105</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G11" s="18">
         <v>0</v>
@@ -2101,10 +2143,10 @@
       <c r="K11" s="15"/>
       <c r="L11" s="15"/>
       <c r="O11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P11" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2116,7 +2158,7 @@
         <v>40</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G12" s="18">
         <v>0</v>
@@ -2134,17 +2176,17 @@
         <v>5882</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E13" s="18"/>
       <c r="F13" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G13" s="18">
         <v>0</v>
@@ -2153,18 +2195,18 @@
         <v>430</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
       <c r="L13" s="15" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="O13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P13" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="76.5">
@@ -2173,10 +2215,10 @@
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
       <c r="E14" s="18" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G14" s="18">
         <v>0</v>
@@ -2185,7 +2227,7 @@
         <v>380754</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
@@ -2197,7 +2239,7 @@
       <c r="C15" s="29"/>
       <c r="D15" s="29"/>
       <c r="E15" s="29" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F15" s="29"/>
       <c r="G15" s="29">
@@ -2207,13 +2249,13 @@
         <v>4770</v>
       </c>
       <c r="I15" s="30" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J15" s="29"/>
       <c r="K15" s="29"/>
       <c r="L15" s="29"/>
       <c r="M15" s="32" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="O15"/>
       <c r="P15"/>
@@ -2226,19 +2268,19 @@
         <v>5646</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G16" s="18">
         <v>0</v>
@@ -2250,7 +2292,7 @@
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
       <c r="L16" s="15" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="O16" t="s">
         <v>23</v>
@@ -2265,10 +2307,10 @@
       <c r="C17" s="29"/>
       <c r="D17" s="29"/>
       <c r="E17" s="29" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G17" s="29">
         <v>0</v>
@@ -2391,16 +2433,16 @@
         <v>29752153</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I2" s="12" t="s">
         <v>22</v>
@@ -2414,25 +2456,25 @@
         <v>18</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D3" s="10">
         <v>29752153</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="106.5">
@@ -2440,28 +2482,28 @@
         <v>105415</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" s="10">
         <v>18383776</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30.75">
@@ -2469,10 +2511,10 @@
         <v>107560</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D5">
         <v>1594882</v>
@@ -2482,7 +2524,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="45.75">
@@ -2499,32 +2541,32 @@
         <v>614042</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:10" ht="30.75">
       <c r="C7" s="2"/>
       <c r="E7" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>41</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I7" s="3"/>
     </row>
@@ -2542,48 +2584,48 @@
         <v>6294159</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I8" s="3"/>
     </row>
     <row r="9" spans="1:10" ht="106.5">
       <c r="C9" s="2"/>
       <c r="E9" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I9" s="3"/>
     </row>
     <row r="10" spans="1:10" ht="45.75">
       <c r="C10" s="2"/>
       <c r="E10" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I10" s="3"/>
     </row>
@@ -2600,28 +2642,28 @@
         <v>132014</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D12">
         <v>1771084</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="45.75">
@@ -2629,41 +2671,41 @@
         <v>141105</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D13">
         <v>821580</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I13" s="6"/>
     </row>
     <row r="14" spans="1:10">
       <c r="C14" s="2"/>
       <c r="E14" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I14" s="6"/>
     </row>
@@ -2672,60 +2714,60 @@
         <v>5882</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15">
         <v>17346000</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="76.5">
       <c r="E16" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="30.75">
       <c r="E17" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="45.75">
@@ -2733,40 +2775,40 @@
         <v>5646</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D18">
         <v>2370000</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I18" s="6"/>
     </row>
     <row r="19" spans="1:9" ht="45.75">
       <c r="E19" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I19" s="6"/>
     </row>
@@ -2814,160 +2856,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="33" t="s">
-        <v>107</v>
+      <c r="A2" s="43" t="s">
+        <v>110</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="33"/>
+      <c r="A3" s="43"/>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="33"/>
+      <c r="A4" s="43"/>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="34" t="s">
-        <v>113</v>
+      <c r="A5" s="44" t="s">
+        <v>116</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="34"/>
+      <c r="A6" s="44"/>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="34"/>
+      <c r="A7" s="44"/>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="34"/>
+      <c r="A8" s="44"/>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="34"/>
+      <c r="A9" s="44"/>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="35" t="s">
-        <v>123</v>
+      <c r="A10" s="45" t="s">
+        <v>126</v>
       </c>
       <c r="B10" t="s">
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="35"/>
+      <c r="A11" s="45"/>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="36" t="s">
-        <v>126</v>
+      <c r="A12" s="46" t="s">
+        <v>129</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="36"/>
+      <c r="A13" s="46"/>
       <c r="B13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C13" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="36"/>
+      <c r="A14" s="46"/>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C14" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B15" t="s">
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/01_Input/00_CO Validation/Bosnia and Herzegovina - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Bosnia and Herzegovina - Energy Projects.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27221"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28318"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="476" documentId="11_7A16C5C5EBEF1110EA3321A633CA6B1980AA3C4F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7CD7F75-88BA-45BC-8023-7BCDF34C8619}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="574" documentId="11_7A16C5C5EBEF1110EA3321A633CA6B1980AA3C4F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50732981-D362-446A-A710-37118E8B0155}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -34,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="159">
   <si>
     <t>Project ID</t>
   </si>
@@ -105,6 +110,9 @@
     <t>http://open.undp.org/projects/00048025</t>
   </si>
   <si>
+    <t>Energy Efficiency Services</t>
+  </si>
+  <si>
     <t>Number of detailed energy audits prepared</t>
   </si>
   <si>
@@ -120,180 +128,196 @@
     <t>Energy Efficiency</t>
   </si>
   <si>
+    <t>Decarbonization</t>
+  </si>
+  <si>
+    <t>Number of public builidings retrofitted</t>
+  </si>
+  <si>
+    <t>Target met in 2022. Energy efficient retrofitting of additional 5 buildings in BIH</t>
+  </si>
+  <si>
+    <t>Incentives and Support</t>
+  </si>
+  <si>
+    <t>Green Economic Development Phase II</t>
+  </si>
+  <si>
+    <t>http://open.undp.org/projects/00105415</t>
+  </si>
+  <si>
+    <t>Number of people who directly benefit from energy efficiency improvements in public infrastructure/buildings, including street lightening.</t>
+  </si>
+  <si>
+    <t>EE retrofit of public buidlings and public lightning sytems</t>
+  </si>
+  <si>
+    <t>Green Deal</t>
+  </si>
+  <si>
+    <t>http://open.undp.org/projects/00131266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of residential households with improved EE </t>
+  </si>
+  <si>
+    <t>Medium Enterprises</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of SMEs with improved EE </t>
+  </si>
+  <si>
+    <t>Green Economic Development Project – III Phase</t>
+  </si>
+  <si>
+    <t>http://open.undp.org/projects/00132013</t>
+  </si>
+  <si>
+    <t>Yevgen: budget corrected as per ProDoc (changed from USD 6 294 159 to USD 16 726 410</t>
+  </si>
+  <si>
+    <t>Electricity Access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of off-grid households in remote areas in BiH </t>
+  </si>
+  <si>
+    <t>Close the gap on energy access</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>Decarbonzation of Residential Sector in Bosnia and Her</t>
+  </si>
+  <si>
+    <t>http://open.undp.org/projects/00132014</t>
+  </si>
+  <si>
+    <t>Number of financial mechanisms developed</t>
+  </si>
+  <si>
+    <t>Development of financial mechanisms on municipal / city level for financing of EE retrofit in residential sector</t>
+  </si>
+  <si>
+    <t>Financing Model</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>36 cities throughout Bosnia and Herzegovina. All 36 have developed SECAPs</t>
+  </si>
+  <si>
+    <t>Number of vulnerable categories, including women, covered by energy efficiency improvement studies</t>
+  </si>
+  <si>
+    <t>Yevgen: added beneficiaries as per the ProDoc</t>
+  </si>
+  <si>
+    <t>Capacity Building Training</t>
+  </si>
+  <si>
+    <t>Number of government representatives (gender disaggregated) with increased capacities in decarbonization of residential sector in Bosnia and Herzegovina</t>
+  </si>
+  <si>
+    <t>Campaign Participant</t>
+  </si>
+  <si>
+    <t>Public awareness campaign outreach (out of which at least 40% women)</t>
+  </si>
+  <si>
+    <t>Inclusive Decarbonization Activity IDA</t>
+  </si>
+  <si>
+    <t>http://open.undp.org/projects/00141105</t>
+  </si>
+  <si>
+    <t>Small Enterprises</t>
+  </si>
+  <si>
+    <t>Number of SMEs with improved EE (decarbonisation)</t>
+  </si>
+  <si>
+    <t>Number of institutions benefiting from increased capacities in decarbonisation of SME Sector</t>
+  </si>
+  <si>
+    <t>De-Risking and Scaling-up Investment in EE</t>
+  </si>
+  <si>
+    <t>https://co.pims.undp.org/project/view?id=5882</t>
+  </si>
+  <si>
+    <t>430 buildings</t>
+  </si>
+  <si>
+    <t>(by the end of 2022 result was 100 public buildings)</t>
+  </si>
+  <si>
+    <t>GCF</t>
+  </si>
+  <si>
+    <t>VF</t>
+  </si>
+  <si>
+    <t>Number of people who directly benefit from energy efficiency improvements in public buildings</t>
+  </si>
+  <si>
+    <t>(by the end of 2022 result was 380754 beneficiaries)</t>
+  </si>
+  <si>
+    <t>(by the end of 2022 result was 4770 trainees)</t>
+  </si>
+  <si>
+    <t>Catalyzing Env.Fin. for Low-Carbon Urban Dev</t>
+  </si>
+  <si>
+    <t>PIMS+</t>
+  </si>
+  <si>
+    <t>Other Energy Services</t>
+  </si>
+  <si>
+    <t>Number of people benefiting from ESCO investments</t>
+  </si>
+  <si>
+    <t>GEF
+BIH Government</t>
+  </si>
+  <si>
+    <t>Number of people benefiting from improved waste management</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>US$29752153</t>
+  </si>
+  <si>
+    <t>Scale up energy finance</t>
+  </si>
+  <si>
     <t>Government Capacity-Building</t>
   </si>
   <si>
-    <t>Regional</t>
-  </si>
-  <si>
-    <t>The subnational/region is undefined</t>
-  </si>
-  <si>
-    <t>Energy Efficiency Services</t>
-  </si>
-  <si>
-    <t>Number of public builidings retrofitted</t>
-  </si>
-  <si>
-    <t>5 buildings</t>
-  </si>
-  <si>
-    <t>Target met in 2022. Energy efficient retrofitting of additional 5 buildings in BIH</t>
-  </si>
-  <si>
-    <t>Green Economic Development Phase II</t>
-  </si>
-  <si>
-    <t>http://open.undp.org/projects/00105415</t>
-  </si>
-  <si>
-    <t>Number of people who directly benefit from energy efficiency improvements in public infrastructure/buildings, including street lightening.</t>
-  </si>
-  <si>
-    <t>EE retrofit of public buidlings and public lightning sytems</t>
-  </si>
-  <si>
-    <t>Green Deal</t>
-  </si>
-  <si>
-    <t>http://open.undp.org/projects/00131266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of residential households with improved EE </t>
-  </si>
-  <si>
-    <t>146 HH</t>
+    <t>US$18383776</t>
+  </si>
+  <si>
+    <t>US$614042</t>
   </si>
   <si>
     <t>251 HH</t>
   </si>
   <si>
-    <t>Medium Enterprises</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of SMEs with improved EE </t>
-  </si>
-  <si>
-    <t>Green Economic Development Project – III Phase</t>
-  </si>
-  <si>
-    <t>http://open.undp.org/projects/00132013</t>
-  </si>
-  <si>
-    <t>40 buildings</t>
-  </si>
-  <si>
-    <t>Electricity Access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of off-grid households in remote areas in BiH </t>
+    <t>US$6294159</t>
   </si>
   <si>
     <t>10 HH</t>
   </si>
   <si>
-    <t>Close the gap on energy access</t>
-  </si>
-  <si>
-    <t>Solar</t>
-  </si>
-  <si>
-    <t>Decarbonzation of Residential Sector in Bosnia and Her</t>
-  </si>
-  <si>
-    <t>http://open.undp.org/projects/00132014</t>
-  </si>
-  <si>
-    <t>Number of financial mechanisms developed</t>
-  </si>
-  <si>
-    <t>Development of financial mechanisms on municipal / city level for financing of EE retrofit in residential sector</t>
-  </si>
-  <si>
-    <t>Financing Model</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>Is it only Sarajevo and Tuzla?</t>
-  </si>
-  <si>
-    <t>Inclusive Decarbonization Activity IDA</t>
-  </si>
-  <si>
-    <t>http://open.undp.org/projects/00141105</t>
-  </si>
-  <si>
-    <t>Small Enterprises</t>
-  </si>
-  <si>
-    <t>Number of SMEs with improved EE (decarbonisation)</t>
-  </si>
-  <si>
-    <t>Number of institutions benefiting from increased capacities in decarbonisation of SME Sector</t>
-  </si>
-  <si>
-    <t>De-Risking and Scaling-up Investment in EE</t>
-  </si>
-  <si>
-    <t>PIMS+</t>
-  </si>
-  <si>
-    <t>430 buildings</t>
-  </si>
-  <si>
-    <t>(by the end of 2022 result was 100 public buildings)</t>
-  </si>
-  <si>
-    <t>VF</t>
-  </si>
-  <si>
-    <t>Number of people who directly benefit from energy efficiency improvements in public buildings</t>
-  </si>
-  <si>
-    <t>(by the end of 2022 result was 380754 beneficiaries)</t>
-  </si>
-  <si>
-    <t>Capacity Building Training</t>
-  </si>
-  <si>
-    <t>(by the end of 2022 result was 4770 trainees)</t>
-  </si>
-  <si>
-    <t>Catalyzing Env.Fin. for Low-Carbon Urban Dev</t>
-  </si>
-  <si>
-    <t>Other Energy Services</t>
-  </si>
-  <si>
-    <t>Number of people benefiting from ESCO investments</t>
-  </si>
-  <si>
-    <t>Number of people benefiting from improved waste management</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>US$29752153</t>
-  </si>
-  <si>
-    <t>Scale up energy finance</t>
-  </si>
-  <si>
-    <t>US$18383776</t>
-  </si>
-  <si>
-    <t>US$614042</t>
-  </si>
-  <si>
-    <t>US$6294159</t>
-  </si>
-  <si>
     <t>US$1771084</t>
   </si>
   <si>
@@ -484,9 +508,6 @@
   </si>
   <si>
     <t xml:space="preserve">Volume of investment (US dollars) leverage removing barriers to private and public investment in clean, reliable, affordable, and sustainable energy solutions and energy efficiency for social infrastructure, productive use of electricity and other services </t>
-  </si>
-  <si>
-    <t>Campaign Participant</t>
   </si>
   <si>
     <t>Individuals who participate in advocacy and campaign on energy</t>
@@ -502,7 +523,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -550,8 +571,16 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -573,6 +602,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -690,17 +731,14 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -717,7 +755,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -731,7 +769,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -750,7 +788,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -763,7 +801,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -781,7 +819,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -813,6 +851,25 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -824,7 +881,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1127,8 +1184,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44EEABE7-4A5A-449C-842C-20FB87CD766D}">
-  <dimension ref="A1:U17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:V20"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="67.5703125" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
@@ -1147,7 +1204,7 @@
     <col min="21" max="21" width="33.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:22">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1212,7 +1269,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="43.5" customHeight="1">
+    <row r="2" spans="1:22" ht="67.5" customHeight="1">
       <c r="A2" s="14">
         <v>48025</v>
       </c>
@@ -1225,122 +1282,126 @@
       <c r="D2" s="14">
         <v>29752153</v>
       </c>
-      <c r="E2" s="13" t="s">
-        <v>19</v>
+      <c r="E2" s="51" t="s">
+        <v>23</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="33">
         <v>0</v>
       </c>
-      <c r="H2" s="33">
-        <v>120</v>
+      <c r="H2" s="50">
+        <v>350</v>
       </c>
       <c r="I2" s="34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="25"/>
       <c r="L2" s="45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" s="33"/>
       <c r="N2" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O2" s="33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P2" s="33"/>
-      <c r="Q2" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="R2" s="33" t="s">
-        <v>27</v>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="50" t="s">
+        <v>29</v>
       </c>
       <c r="S2" s="47"/>
-      <c r="T2" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="U2" s="47" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="50.25" customHeight="1">
+      <c r="T2" s="33"/>
+      <c r="U2" s="47"/>
+    </row>
+    <row r="3" spans="1:22" ht="50.25" customHeight="1">
       <c r="A3" s="14"/>
       <c r="B3" s="14"/>
       <c r="C3" s="31"/>
       <c r="E3" s="48" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F3" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G3" s="36">
         <v>0</v>
       </c>
-      <c r="H3" s="36" t="s">
-        <v>33</v>
+      <c r="H3" s="52">
+        <v>125</v>
       </c>
       <c r="I3" s="34" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J3" s="13"/>
       <c r="K3" s="13"/>
       <c r="L3" s="45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M3" s="33"/>
       <c r="N3" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" s="33"/>
+        <v>27</v>
+      </c>
+      <c r="O3" s="33" t="s">
+        <v>28</v>
+      </c>
       <c r="P3" s="33"/>
-      <c r="Q3" s="33"/>
-      <c r="R3" s="33"/>
+      <c r="Q3" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" s="50" t="s">
+        <v>29</v>
+      </c>
       <c r="S3" s="47"/>
       <c r="T3" s="33"/>
       <c r="U3" s="47"/>
     </row>
-    <row r="4" spans="1:21" ht="106.5">
+    <row r="4" spans="1:22" ht="86.45">
       <c r="A4" s="14">
         <v>105415</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D4" s="14">
         <v>18383776</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="33">
+        <v>35</v>
+      </c>
+      <c r="G4" s="50">
         <v>567</v>
       </c>
-      <c r="H4" s="33">
+      <c r="H4" s="50">
         <v>2698</v>
       </c>
       <c r="I4" s="34" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
+      <c r="K4" s="13">
+        <v>51</v>
+      </c>
       <c r="L4" s="45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M4" s="33"/>
       <c r="N4" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" s="33"/>
+        <v>27</v>
+      </c>
+      <c r="O4" s="33" t="s">
+        <v>28</v>
+      </c>
       <c r="P4" s="33"/>
       <c r="Q4" s="33"/>
       <c r="R4" s="33"/>
@@ -1348,40 +1409,40 @@
       <c r="T4" s="33"/>
       <c r="U4" s="47"/>
     </row>
-    <row r="5" spans="1:21" ht="45.75">
+    <row r="5" spans="1:22" ht="43.15">
       <c r="A5" s="13">
         <v>131266</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D5" s="13">
         <v>614042</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>43</v>
+        <v>39</v>
+      </c>
+      <c r="G5" s="53">
+        <v>0</v>
+      </c>
+      <c r="H5" s="53">
+        <v>251</v>
       </c>
       <c r="I5" s="13"/>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
       <c r="L5" s="45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M5" s="33"/>
       <c r="N5" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O5" s="33"/>
       <c r="P5" s="33"/>
@@ -1391,32 +1452,32 @@
       <c r="T5" s="33"/>
       <c r="U5" s="47"/>
     </row>
-    <row r="6" spans="1:21" ht="30.75">
+    <row r="6" spans="1:22" ht="28.9">
       <c r="A6" s="13"/>
       <c r="B6" s="13"/>
       <c r="C6" s="37"/>
       <c r="D6" s="13"/>
       <c r="E6" s="13" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="13">
+        <v>41</v>
+      </c>
+      <c r="G6" s="53">
         <v>0</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="53">
         <v>15</v>
       </c>
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
       <c r="L6" s="45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M6" s="33"/>
       <c r="N6" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O6" s="33"/>
       <c r="P6" s="33"/>
@@ -1426,40 +1487,40 @@
       <c r="T6" s="33"/>
       <c r="U6" s="47"/>
     </row>
-    <row r="7" spans="1:21" ht="30.75">
+    <row r="7" spans="1:22" ht="28.9">
       <c r="A7" s="13">
         <v>132013</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D7" s="13">
-        <v>6294159</v>
+        <v>16726410</v>
       </c>
       <c r="E7" s="48" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G7" s="13">
         <v>0</v>
       </c>
-      <c r="H7" s="13" t="s">
-        <v>48</v>
+      <c r="H7" s="57">
+        <v>82</v>
       </c>
       <c r="I7" s="13"/>
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
       <c r="L7" s="45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M7" s="33"/>
       <c r="N7" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O7" s="33"/>
       <c r="P7" s="33"/>
@@ -1468,17 +1529,20 @@
       <c r="S7" s="47"/>
       <c r="T7" s="33"/>
       <c r="U7" s="47"/>
-    </row>
-    <row r="8" spans="1:21" ht="106.5">
+      <c r="V7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="86.45">
       <c r="A8" s="13"/>
       <c r="B8" s="13"/>
       <c r="C8" s="37"/>
       <c r="D8" s="13"/>
       <c r="E8" s="48" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G8" s="13">
         <v>0</v>
@@ -1490,11 +1554,11 @@
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
       <c r="L8" s="45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M8" s="33"/>
       <c r="N8" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O8" s="33"/>
       <c r="P8" s="33"/>
@@ -1504,52 +1568,52 @@
       <c r="T8" s="33"/>
       <c r="U8" s="47"/>
     </row>
-    <row r="9" spans="1:21" ht="45.75">
+    <row r="9" spans="1:22" ht="43.15">
       <c r="A9" s="13"/>
       <c r="B9" s="13"/>
       <c r="C9" s="37"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G9" s="13">
         <v>0</v>
       </c>
-      <c r="H9" s="13" t="s">
-        <v>51</v>
+      <c r="H9" s="53">
+        <v>30</v>
       </c>
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
       <c r="L9" s="45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M9" s="33"/>
       <c r="N9" s="46" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="O9" s="33"/>
       <c r="P9" s="33"/>
       <c r="Q9" s="33"/>
       <c r="R9" s="33"/>
       <c r="S9" s="47" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="T9" s="33"/>
       <c r="U9" s="47"/>
     </row>
-    <row r="10" spans="1:21" ht="60.75">
+    <row r="10" spans="1:22" ht="60.75">
       <c r="A10" s="13">
         <v>132014</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="37" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>50</v>
       </c>
       <c r="D10" s="13">
         <v>1771084</v>
@@ -1558,7 +1622,7 @@
         <v>19</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G10" s="13">
         <v>0</v>
@@ -1567,69 +1631,59 @@
         <v>36</v>
       </c>
       <c r="I10" s="35" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M10" s="33"/>
       <c r="N10" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O10" s="33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P10" s="33"/>
       <c r="Q10" s="33" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="R10" s="33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S10" s="47"/>
       <c r="T10" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="U10" s="47" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="45.75">
-      <c r="A11" s="13">
-        <v>141105</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="13">
-        <v>821580</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="U10" s="54" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="76.5">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="13"/>
       <c r="E11" s="13" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="G11" s="13">
         <v>0</v>
       </c>
       <c r="H11" s="13">
-        <v>20</v>
+        <v>1500</v>
       </c>
       <c r="I11" s="35"/>
       <c r="J11" s="13"/>
       <c r="K11" s="13"/>
-      <c r="L11" s="45" t="s">
-        <v>25</v>
-      </c>
+      <c r="L11" s="45"/>
       <c r="M11" s="33"/>
       <c r="N11" s="46" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="O11" s="33"/>
       <c r="P11" s="33"/>
@@ -1637,34 +1691,35 @@
       <c r="R11" s="33"/>
       <c r="S11" s="47"/>
       <c r="T11" s="33"/>
-      <c r="U11" s="47"/>
-    </row>
-    <row r="12" spans="1:21" ht="30.75">
+      <c r="U11" s="54"/>
+      <c r="V11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="106.5">
       <c r="A12" s="13"/>
       <c r="B12" s="13"/>
-      <c r="C12" s="37"/>
+      <c r="C12" s="56"/>
       <c r="D12" s="13"/>
       <c r="E12" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>65</v>
+        <v>58</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>59</v>
       </c>
       <c r="G12" s="13">
         <v>0</v>
       </c>
       <c r="H12" s="13">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="I12" s="35"/>
       <c r="J12" s="13"/>
       <c r="K12" s="13"/>
-      <c r="L12" s="45" t="s">
-        <v>25</v>
-      </c>
+      <c r="L12" s="45"/>
       <c r="M12" s="33"/>
       <c r="N12" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O12" s="33"/>
       <c r="P12" s="33"/>
@@ -1672,44 +1727,35 @@
       <c r="R12" s="33"/>
       <c r="S12" s="47"/>
       <c r="T12" s="33"/>
-      <c r="U12" s="47"/>
-    </row>
-    <row r="13" spans="1:21" ht="30.75">
-      <c r="A13" s="13">
-        <v>5882</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="13">
-        <v>17346000</v>
-      </c>
-      <c r="E13" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>32</v>
+      <c r="U12" s="54"/>
+      <c r="V12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="60.75">
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="35" t="s">
+        <v>61</v>
       </c>
       <c r="G13" s="13">
         <v>0</v>
       </c>
-      <c r="H13" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="I13" s="35" t="s">
-        <v>69</v>
-      </c>
+      <c r="H13" s="13">
+        <v>40000</v>
+      </c>
+      <c r="I13" s="35"/>
       <c r="J13" s="13"/>
       <c r="K13" s="13"/>
-      <c r="L13" s="45" t="s">
-        <v>70</v>
-      </c>
+      <c r="L13" s="45"/>
       <c r="M13" s="33"/>
       <c r="N13" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O13" s="33"/>
       <c r="P13" s="33"/>
@@ -1717,36 +1763,45 @@
       <c r="R13" s="33"/>
       <c r="S13" s="47"/>
       <c r="T13" s="33"/>
-      <c r="U13" s="47"/>
-    </row>
-    <row r="14" spans="1:21" ht="76.5">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="38" t="s">
-        <v>71</v>
+      <c r="U13" s="54"/>
+      <c r="V13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="45.75">
+      <c r="A14" s="13">
+        <v>141105</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="13">
+        <v>821580</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="35" t="s">
+        <v>65</v>
       </c>
       <c r="G14" s="13">
         <v>0</v>
       </c>
       <c r="H14" s="13">
-        <v>380754</v>
-      </c>
-      <c r="I14" s="35" t="s">
-        <v>72</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I14" s="35"/>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
       <c r="L14" s="45" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="M14" s="33"/>
       <c r="N14" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O14" s="33"/>
       <c r="P14" s="33"/>
@@ -1756,32 +1811,32 @@
       <c r="T14" s="33"/>
       <c r="U14" s="47"/>
     </row>
-    <row r="15" spans="1:21" s="29" customFormat="1" ht="30.75">
+    <row r="15" spans="1:22" ht="28.9">
       <c r="A15" s="13"/>
       <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
+      <c r="C15" s="37"/>
       <c r="D15" s="13"/>
       <c r="E15" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="F15" s="13"/>
+        <v>40</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>66</v>
+      </c>
       <c r="G15" s="13">
         <v>0</v>
       </c>
       <c r="H15" s="13">
-        <v>4770</v>
-      </c>
-      <c r="I15" s="35" t="s">
-        <v>74</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I15" s="35"/>
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
       <c r="L15" s="45" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="M15" s="33"/>
       <c r="N15" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O15" s="33"/>
       <c r="P15" s="33"/>
@@ -1791,40 +1846,44 @@
       <c r="T15" s="33"/>
       <c r="U15" s="47"/>
     </row>
-    <row r="16" spans="1:21" ht="45.75">
+    <row r="16" spans="1:22" ht="28.9">
       <c r="A16" s="13">
-        <v>5646</v>
+        <v>5882</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="13" t="s">
         <v>67</v>
       </c>
+      <c r="C16" s="49" t="s">
+        <v>68</v>
+      </c>
       <c r="D16" s="13">
-        <v>2370000</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" s="35" t="s">
-        <v>77</v>
+        <v>17346000</v>
+      </c>
+      <c r="E16" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>30</v>
       </c>
       <c r="G16" s="13">
         <v>0</v>
       </c>
-      <c r="H16" s="13">
-        <v>67826</v>
-      </c>
-      <c r="I16" s="35"/>
-      <c r="J16" s="13"/>
+      <c r="H16" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>71</v>
+      </c>
       <c r="K16" s="13"/>
       <c r="L16" s="45" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M16" s="33"/>
       <c r="N16" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O16" s="33"/>
       <c r="P16" s="33"/>
@@ -1834,32 +1893,36 @@
       <c r="T16" s="33"/>
       <c r="U16" s="47"/>
     </row>
-    <row r="17" spans="1:21" s="29" customFormat="1" ht="45.75">
+    <row r="17" spans="1:21" ht="72">
       <c r="A17" s="13"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
-      <c r="E17" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17" s="35" t="s">
-        <v>78</v>
+      <c r="E17" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>73</v>
       </c>
       <c r="G17" s="13">
         <v>0</v>
       </c>
       <c r="H17" s="13">
-        <v>360000</v>
-      </c>
-      <c r="I17" s="35"/>
-      <c r="J17" s="13"/>
+        <v>380754</v>
+      </c>
+      <c r="I17" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>71</v>
+      </c>
       <c r="K17" s="13"/>
       <c r="L17" s="45" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M17" s="33"/>
       <c r="N17" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O17" s="33"/>
       <c r="P17" s="33"/>
@@ -1869,36 +1932,155 @@
       <c r="T17" s="33"/>
       <c r="U17" s="47"/>
     </row>
+    <row r="18" spans="1:21" s="29" customFormat="1" ht="28.9">
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13">
+        <v>0</v>
+      </c>
+      <c r="H18" s="13">
+        <v>4770</v>
+      </c>
+      <c r="I18" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="K18" s="13"/>
+      <c r="L18" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="M18" s="33"/>
+      <c r="N18" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="O18" s="33"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="33"/>
+      <c r="S18" s="47"/>
+      <c r="T18" s="33"/>
+      <c r="U18" s="47"/>
+    </row>
+    <row r="19" spans="1:21" ht="57.6">
+      <c r="A19" s="13">
+        <v>5646</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="13">
+        <v>2370000</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="13">
+        <v>0</v>
+      </c>
+      <c r="H19" s="13">
+        <v>67826</v>
+      </c>
+      <c r="I19" s="35"/>
+      <c r="J19" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="K19" s="13"/>
+      <c r="L19" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="M19" s="33"/>
+      <c r="N19" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" s="33"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="33"/>
+      <c r="R19" s="33"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="33"/>
+      <c r="U19" s="47"/>
+    </row>
+    <row r="20" spans="1:21" s="29" customFormat="1" ht="57.6">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="G20" s="13">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13">
+        <v>360000</v>
+      </c>
+      <c r="I20" s="35"/>
+      <c r="J20" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="K20" s="13"/>
+      <c r="L20" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="M20" s="33"/>
+      <c r="N20" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20" s="33"/>
+      <c r="P20" s="33"/>
+      <c r="Q20" s="33"/>
+      <c r="R20" s="33"/>
+      <c r="S20" s="47"/>
+      <c r="T20" s="33"/>
+      <c r="U20" s="47"/>
+    </row>
   </sheetData>
   <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O18:P21" xr:uid="{8D1D8E1A-CD3D-488D-9A00-54F5E8746A5E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O21:P24" xr:uid="{8D1D8E1A-CD3D-488D-9A00-54F5E8746A5E}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R18:R21 Q2:Q17" xr:uid="{459AA2B0-6C57-4070-9B1C-06D87B7E42F3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R21:R24 Q2:Q20" xr:uid="{459AA2B0-6C57-4070-9B1C-06D87B7E42F3}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q18:Q21 P2:P17" xr:uid="{88E9A924-FBA8-4DDF-826B-B035BF57FF12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q21:Q24 P2:P20" xr:uid="{88E9A924-FBA8-4DDF-826B-B035BF57FF12}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N21" xr:uid="{74E238FC-A409-4C00-BAF6-7C74468BD96F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N24" xr:uid="{74E238FC-A409-4C00-BAF6-7C74468BD96F}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O17" xr:uid="{F9E89E38-69E7-4ABC-AA5B-033C0D49C91B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O20" xr:uid="{F9E89E38-69E7-4ABC-AA5B-033C0D49C91B}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L17" xr:uid="{C0F331D3-75B3-4425-A9E9-49CBA020E08F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L20" xr:uid="{C0F331D3-75B3-4425-A9E9-49CBA020E08F}">
       <formula1>"Non-VF, VF"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M17" xr:uid="{4085724D-038F-43CB-A5F1-459D3CF7A462}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M20" xr:uid="{4085724D-038F-43CB-A5F1-459D3CF7A462}">
       <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T17" xr:uid="{16F80B46-1A05-4818-B5F0-5EF8427434C5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T20" xr:uid="{16F80B46-1A05-4818-B5F0-5EF8427434C5}">
       <formula1>"National, Regional, City, Community"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S17" xr:uid="{7ED79492-61AC-4974-B369-1552353B3AE0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S20" xr:uid="{7ED79492-61AC-4974-B369-1552353B3AE0}">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Other, Unknown"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R17" xr:uid="{AD7208B8-A06F-4F90-8322-57E3801913B7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R20" xr:uid="{AD7208B8-A06F-4F90-8322-57E3801913B7}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1908,7 +2090,8 @@
     <hyperlink ref="C5" r:id="rId3" xr:uid="{F75471AE-8842-4802-8705-58D06EF21545}"/>
     <hyperlink ref="C7" r:id="rId4" xr:uid="{7A5E61FF-1E81-44DB-9CFA-D0DB067391A2}"/>
     <hyperlink ref="C10" r:id="rId5" xr:uid="{2EF3703E-7CCB-4F24-AE6C-2D71F3EEE8C8}"/>
-    <hyperlink ref="C11" r:id="rId6" xr:uid="{F99D1CDD-1CE8-407E-B850-F1E7D7337993}"/>
+    <hyperlink ref="C14" r:id="rId6" xr:uid="{F99D1CDD-1CE8-407E-B850-F1E7D7337993}"/>
+    <hyperlink ref="C16" r:id="rId7" xr:uid="{25619C84-78DD-4E95-9F36-29D5B27A1032}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -1918,13 +2101,13 @@
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>E18:E33</xm:sqref>
+          <xm:sqref>E21:E36</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{07C56E86-29CC-4051-A603-A6171023CDCF}">
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E17</xm:sqref>
+          <xm:sqref>E2:E20</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1935,7 +2118,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D17C48C-31E7-4CC3-8A67-A314C1BD7F13}">
   <dimension ref="A1:S17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="67.5703125" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
@@ -1986,10 +2169,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="23" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O1" s="26" t="s">
         <v>13</v>
@@ -2018,13 +2201,13 @@
         <v>22</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="18">
         <v>0</v>
@@ -2033,22 +2216,22 @@
         <v>120</v>
       </c>
       <c r="I2" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="25"/>
       <c r="L2" s="25"/>
       <c r="O2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="R2" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="S2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="50.25" customHeight="1">
@@ -2058,7 +2241,7 @@
       <c r="D3" s="14"/>
       <c r="E3" s="16"/>
       <c r="F3" s="20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G3" s="21">
         <v>0</v>
@@ -2067,30 +2250,30 @@
         <v>5</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J3" s="13"/>
       <c r="K3" s="13"/>
       <c r="L3" s="13"/>
     </row>
-    <row r="4" spans="1:19" ht="106.5">
+    <row r="4" spans="1:19" ht="86.45">
       <c r="A4" s="14">
         <v>105415</v>
       </c>
       <c r="B4" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="20" t="s">
         <v>35</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>37</v>
       </c>
       <c r="G4" s="18">
         <v>567</v>
@@ -2099,64 +2282,64 @@
         <v>2698</v>
       </c>
       <c r="I4" s="19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="45.75">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="43.15">
       <c r="A5" s="13">
         <v>131266</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>39</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>41</v>
       </c>
       <c r="G5" s="16">
         <v>146</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="30.75">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="28.9">
       <c r="A6" s="13"/>
       <c r="B6" s="13"/>
       <c r="C6" s="22"/>
       <c r="D6" s="13"/>
       <c r="E6" s="16" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G6" s="16">
         <v>0</v>
@@ -2169,24 +2352,24 @@
       <c r="K6" s="13"/>
       <c r="L6" s="13"/>
     </row>
-    <row r="7" spans="1:19" ht="30.75">
+    <row r="7" spans="1:19" ht="28.9">
       <c r="A7" s="13">
         <v>132013</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G7" s="16">
         <v>0</v>
@@ -2199,22 +2382,22 @@
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
       <c r="O7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="106.5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="86.45">
       <c r="A8" s="13"/>
       <c r="B8" s="13"/>
       <c r="C8" s="22"/>
       <c r="D8" s="13"/>
       <c r="E8" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G8" s="16">
         <v>0</v>
@@ -2227,46 +2410,46 @@
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
     </row>
-    <row r="9" spans="1:19" ht="45.75">
+    <row r="9" spans="1:19" ht="43.15">
       <c r="A9" s="13"/>
       <c r="B9" s="13"/>
       <c r="C9" s="22"/>
       <c r="D9" s="13"/>
       <c r="E9" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G9" s="16">
         <v>0</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
       <c r="L9" s="13"/>
     </row>
-    <row r="10" spans="1:19" ht="60.75">
+    <row r="10" spans="1:19" ht="43.15">
       <c r="A10" s="13">
         <v>132014</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>19</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G10" s="16">
         <v>0</v>
@@ -2275,42 +2458,42 @@
         <v>36</v>
       </c>
       <c r="I10" s="20" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
       <c r="O10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R10" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="S10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="45.75">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="43.15">
       <c r="A11" s="13">
         <v>141105</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G11" s="16">
         <v>0</v>
@@ -2323,10 +2506,10 @@
       <c r="K11" s="13"/>
       <c r="L11" s="13"/>
       <c r="O11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2335,10 +2518,10 @@
       <c r="C12" s="22"/>
       <c r="D12" s="13"/>
       <c r="E12" s="16" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G12" s="16">
         <v>0</v>
@@ -2351,22 +2534,22 @@
       <c r="K12" s="13"/>
       <c r="L12" s="13"/>
     </row>
-    <row r="13" spans="1:19" ht="30.75">
+    <row r="13" spans="1:19" ht="28.9">
       <c r="A13" s="13">
         <v>5882</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E13" s="16"/>
       <c r="F13" s="20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G13" s="16">
         <v>0</v>
@@ -2375,30 +2558,30 @@
         <v>430</v>
       </c>
       <c r="I13" s="20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J13" s="13"/>
       <c r="K13" s="13"/>
       <c r="L13" s="13" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="O13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="76.5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="72">
       <c r="A14" s="13"/>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
       <c r="E14" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G14" s="16">
         <v>0</v>
@@ -2407,19 +2590,19 @@
         <v>380754</v>
       </c>
       <c r="I14" s="20" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
       <c r="L14" s="13"/>
     </row>
-    <row r="15" spans="1:19" s="29" customFormat="1" ht="30.75">
+    <row r="15" spans="1:19" s="29" customFormat="1" ht="28.9">
       <c r="A15" s="27"/>
       <c r="B15" s="27"/>
       <c r="C15" s="27"/>
       <c r="D15" s="27"/>
       <c r="E15" s="27" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F15" s="27"/>
       <c r="G15" s="27">
@@ -2429,13 +2612,13 @@
         <v>4770</v>
       </c>
       <c r="I15" s="28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J15" s="27"/>
       <c r="K15" s="27"/>
       <c r="L15" s="27"/>
       <c r="M15" s="30" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="O15"/>
       <c r="P15"/>
@@ -2443,24 +2626,24 @@
       <c r="R15"/>
       <c r="S15"/>
     </row>
-    <row r="16" spans="1:19" ht="45.75">
+    <row r="16" spans="1:19" ht="43.15">
       <c r="A16" s="13">
         <v>5646</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G16" s="16">
         <v>0</v>
@@ -2472,25 +2655,25 @@
       <c r="J16" s="13"/>
       <c r="K16" s="13"/>
       <c r="L16" s="13" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="O16" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" s="29" customFormat="1" ht="45.75">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" s="29" customFormat="1" ht="43.15">
       <c r="A17" s="27"/>
       <c r="B17" s="27"/>
       <c r="C17" s="27"/>
       <c r="D17" s="27"/>
       <c r="E17" s="27" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G17" s="27">
         <v>0</v>
@@ -2503,10 +2686,10 @@
       <c r="K17" s="27"/>
       <c r="L17" s="27"/>
       <c r="O17" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P17" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="Q17"/>
       <c r="R17"/>
@@ -2557,7 +2740,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="67.5703125" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
@@ -2613,19 +2796,19 @@
         <v>29752153</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="50.25" customHeight="1">
@@ -2636,65 +2819,65 @@
         <v>21</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D3" s="8">
         <v>29752153</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="106.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="86.45">
       <c r="A4" s="8">
         <v>105415</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D4" s="8">
         <v>18383776</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="30.75">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="28.9">
       <c r="A5">
         <v>107560</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D5">
         <v>1594882</v>
@@ -2704,108 +2887,108 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="45.75">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="43.15">
       <c r="A6">
         <v>131266</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D6">
         <v>614042</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="1:10" ht="30.75">
+    <row r="7" spans="1:10" ht="28.9">
       <c r="C7" s="2"/>
       <c r="E7" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:10" ht="30.75">
+    <row r="8" spans="1:10" ht="28.9">
       <c r="A8">
         <v>132013</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D8">
         <v>6294159</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="I8" s="3"/>
     </row>
-    <row r="9" spans="1:10" ht="106.5">
+    <row r="9" spans="1:10" ht="86.45">
       <c r="C9" s="2"/>
       <c r="E9" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="I9" s="3"/>
     </row>
-    <row r="10" spans="1:10" ht="45.75">
+    <row r="10" spans="1:10" ht="43.15">
       <c r="C10" s="2"/>
       <c r="E10" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="I10" s="3"/>
     </row>
@@ -2817,178 +3000,178 @@
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:10" ht="60.75">
+    <row r="12" spans="1:10" ht="43.15">
       <c r="A12">
         <v>132014</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D12">
         <v>1771084</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="45.75">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="43.15">
       <c r="A13">
         <v>141105</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13">
         <v>821580</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:10">
       <c r="C14" s="2"/>
       <c r="E14" s="3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:10" ht="30.75">
+    <row r="15" spans="1:10" ht="28.9">
       <c r="A15">
         <v>5882</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D15">
         <v>17346000</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="76.5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="72">
       <c r="E16" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="30.75">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="28.9">
       <c r="E17" s="3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="45.75">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="43.15">
       <c r="A18">
         <v>5646</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D18">
         <v>2370000</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="45.75">
+    <row r="19" spans="1:9" ht="43.15">
       <c r="E19" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I19" s="4"/>
     </row>
@@ -3029,7 +3212,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="2" width="52.7109375" customWidth="1"/>
   </cols>
@@ -3042,172 +3225,172 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="49" t="s">
-        <v>49</v>
+    <row r="2" spans="1:2" ht="43.15">
+      <c r="A2" s="58" t="s">
+        <v>45</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="49" t="s">
-        <v>121</v>
+      <c r="A3" s="58" t="s">
+        <v>127</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="49" t="s">
-        <v>123</v>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="28.9">
+      <c r="A4" s="58" t="s">
+        <v>129</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="49" t="s">
-        <v>125</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="28.9">
+      <c r="A5" s="58" t="s">
+        <v>131</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="49" t="s">
-        <v>127</v>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="86.45">
+      <c r="A6" s="58" t="s">
+        <v>133</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="49" t="s">
-        <v>129</v>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="43.15">
+      <c r="A7" s="58" t="s">
+        <v>135</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="49" t="s">
-        <v>131</v>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="43.15">
+      <c r="A8" s="58" t="s">
+        <v>137</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="49" t="s">
-        <v>133</v>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="43.15">
+      <c r="A9" s="58" t="s">
+        <v>139</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="B10" s="50" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="50" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="49" t="s">
-        <v>138</v>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="28.9">
+      <c r="A10" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" s="59" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="28.9">
+      <c r="A11" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="59" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="43.15">
+      <c r="A12" s="58" t="s">
+        <v>144</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="B13" s="50" t="s">
-        <v>140</v>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="28.9">
+      <c r="A13" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="59" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="49" t="s">
-        <v>141</v>
-      </c>
-      <c r="B14" s="50" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="50" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="50" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="49" t="s">
-        <v>73</v>
+      <c r="A14" s="58" t="s">
+        <v>147</v>
+      </c>
+      <c r="B14" s="59" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="28.9">
+      <c r="A15" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="59" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="28.9">
+      <c r="A16" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="59" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="28.9">
+      <c r="A17" s="58" t="s">
+        <v>58</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="B18" s="50" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="49" t="s">
-        <v>148</v>
-      </c>
-      <c r="B19" s="50" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="B20" s="50" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="49" t="s">
+    <row r="18" spans="1:2" ht="28.9">
+      <c r="A18" s="58" t="s">
+        <v>152</v>
+      </c>
+      <c r="B18" s="59" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="72">
+      <c r="A19" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="B19" s="59" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="28.9">
+      <c r="A20" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="59" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="43.15">
+      <c r="A21" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="51" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="B22" s="50" t="s">
-        <v>153</v>
+      <c r="B21" s="60" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="28.9">
+      <c r="A22" s="58" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="59" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -3225,8 +3408,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -3251,6 +3434,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3330,6 +3514,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -3489,7 +3678,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{291EA098-7E97-4E7A-A6FA-7E36F3FE1370}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93BBB155-B0CB-44FE-AC54-4FAB12F0C100}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/01_Input/00_CO Validation/Bosnia and Herzegovina - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Bosnia and Herzegovina - Energy Projects.xlsx
@@ -237,7 +237,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -387,9 +387,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -471,6 +468,46 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K7" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L7" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K11" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L11" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K18" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L18" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1217,15 +1254,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K7" s="53" t="n">
+      <c r="K7" s="62" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="62" t="n"/>
-      <c r="M7" s="62" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M7" s="13" t="n"/>
       <c r="N7" s="13" t="n"/>
       <c r="O7" s="13" t="n"/>
       <c r="P7" s="33" t="n"/>
@@ -1408,15 +1441,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K11" s="13" t="n">
+      <c r="K11" s="62" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="62" t="n"/>
-      <c r="M11" s="62" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M11" s="13" t="n"/>
       <c r="N11" s="13" t="n"/>
       <c r="O11" s="13" t="n"/>
       <c r="P11" s="33" t="n"/>
@@ -1771,15 +1800,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K18" s="13" t="n">
+      <c r="K18" s="62" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="62" t="n"/>
-      <c r="M18" s="63" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M18" s="35" t="n"/>
       <c r="N18" s="13" t="n"/>
       <c r="O18" s="13" t="n"/>
       <c r="P18" s="33" t="n"/>
@@ -2067,7 +2092,7 @@
       <c r="X23" s="47" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="13">
+  <dataValidations count="11">
     <dataValidation sqref="O21:P24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
     </dataValidation>
@@ -2101,12 +2126,6 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
@@ -2115,6 +2134,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3614,288 +3634,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="64" t="inlineStr">
+      <c r="A1" s="63" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="64" t="inlineStr">
+      <c r="B1" s="63" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
     </row>
     <row r="2" ht="43.15" customHeight="1">
-      <c r="A2" s="65" t="inlineStr">
+      <c r="A2" s="64" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="B2" s="65" t="inlineStr">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="65" t="inlineStr">
+      <c r="A3" s="64" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="B3" s="65" t="inlineStr">
+      <c r="B3" s="64" t="inlineStr">
         <is>
           <t>Installed renewable or clean-energy power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28.9" customHeight="1">
-      <c r="A4" s="65" t="inlineStr">
+      <c r="A4" s="64" t="inlineStr">
         <is>
           <t>Energy Storage (MW)</t>
         </is>
       </c>
-      <c r="B4" s="65" t="inlineStr">
+      <c r="B4" s="64" t="inlineStr">
         <is>
           <t>Installed energy storage power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28.9" customHeight="1">
-      <c r="A5" s="65" t="inlineStr">
+      <c r="A5" s="64" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="B5" s="65" t="inlineStr">
+      <c r="B5" s="64" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="86.45" customHeight="1">
-      <c r="A6" s="65" t="inlineStr">
+      <c r="A6" s="64" t="inlineStr">
         <is>
           <t>Clean Heating</t>
         </is>
       </c>
-      <c r="B6" s="65" t="inlineStr">
+      <c r="B6" s="64" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="43.15" customHeight="1">
-      <c r="A7" s="65" t="inlineStr">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="B7" s="65" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean, affordable, and sustainable energy for agricultural and food-system activities.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="43.15" customHeight="1">
-      <c r="A8" s="65" t="inlineStr">
+      <c r="A8" s="64" t="inlineStr">
         <is>
           <t>Health Services</t>
         </is>
       </c>
-      <c r="B8" s="65" t="inlineStr">
+      <c r="B8" s="64" t="inlineStr">
         <is>
           <t>Number of people who gain access to health care facilities through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="43.15" customHeight="1">
-      <c r="A9" s="65" t="inlineStr">
+      <c r="A9" s="64" t="inlineStr">
         <is>
           <t>Water Services</t>
         </is>
       </c>
-      <c r="B9" s="65" t="inlineStr">
+      <c r="B9" s="64" t="inlineStr">
         <is>
           <t>Number of people who gain access to water services through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28.9" customHeight="1">
-      <c r="A10" s="65" t="inlineStr">
+      <c r="A10" s="64" t="inlineStr">
         <is>
           <t>Education Services</t>
         </is>
       </c>
-      <c r="B10" s="65" t="inlineStr">
+      <c r="B10" s="64" t="inlineStr">
         <is>
           <t>Number of people who gain access to education services through clean energy systems, including students and teachers.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28.9" customHeight="1">
-      <c r="A11" s="65" t="inlineStr">
+      <c r="A11" s="64" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="B11" s="65" t="inlineStr">
+      <c r="B11" s="64" t="inlineStr">
         <is>
           <t>Number of people served or energy saved from transport and e-mobility interventions, such as electric vehicles or charging stations.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="43.15" customHeight="1">
-      <c r="A12" s="65" t="inlineStr">
+      <c r="A12" s="64" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
         </is>
       </c>
-      <c r="B12" s="65" t="inlineStr">
+      <c r="B12" s="64" t="inlineStr">
         <is>
           <t>Energy saved from energy-efficiency interventions, such as building or industrial efficiency.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28.9" customHeight="1">
-      <c r="A13" s="65" t="inlineStr">
+      <c r="A13" s="64" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
         </is>
       </c>
-      <c r="B13" s="65" t="inlineStr">
+      <c r="B13" s="64" t="inlineStr">
         <is>
           <t>Number of people benefiting from energy infrastructure interventions, such as streetlights, transmission, and distribution lines.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="65" t="inlineStr">
+      <c r="A14" s="64" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
         </is>
       </c>
-      <c r="B14" s="65" t="inlineStr">
+      <c r="B14" s="64" t="inlineStr">
         <is>
           <t>Access to other energy services not captured by the categories above.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28.9" customHeight="1">
-      <c r="A15" s="65" t="inlineStr">
+      <c r="A15" s="64" t="inlineStr">
         <is>
           <t>Financing support</t>
         </is>
       </c>
-      <c r="B15" s="65" t="inlineStr">
+      <c r="B15" s="64" t="inlineStr">
         <is>
           <t>Support for the development of the energy market ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28.9" customHeight="1">
-      <c r="A16" s="65" t="inlineStr">
+      <c r="A16" s="64" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
         </is>
       </c>
-      <c r="B16" s="65" t="inlineStr">
+      <c r="B16" s="64" t="inlineStr">
         <is>
           <t>Support for the development of medium enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28.9" customHeight="1">
-      <c r="A17" s="65" t="inlineStr">
+      <c r="A17" s="64" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
         </is>
       </c>
-      <c r="B17" s="65" t="inlineStr">
+      <c r="B17" s="64" t="inlineStr">
         <is>
           <t>Support for the development of small enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28.9" customHeight="1">
-      <c r="A18" s="65" t="inlineStr">
+      <c r="A18" s="64" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="B18" s="65" t="inlineStr">
+      <c r="B18" s="64" t="inlineStr">
         <is>
           <t>Number of people benefiting from training on energy business, energy finance, or related implementation capacity.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="72" customHeight="1">
-      <c r="A19" s="65" t="inlineStr">
+      <c r="A19" s="64" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
         </is>
       </c>
-      <c r="B19" s="65" t="inlineStr">
+      <c r="B19" s="64" t="inlineStr">
         <is>
           <t>Training for enterprises on the energy business, assumed to result in direct beneficiaries.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28.9" customHeight="1">
-      <c r="A20" s="65" t="inlineStr">
+      <c r="A20" s="64" t="inlineStr">
         <is>
           <t>Market Intervention</t>
         </is>
       </c>
-      <c r="B20" s="65" t="inlineStr">
+      <c r="B20" s="64" t="inlineStr">
         <is>
           <t>Volume of investment leveraged or barriers removed for clean, reliable, affordable, and sustainable energy solutions.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="43.15" customHeight="1">
-      <c r="A21" s="65" t="inlineStr">
+      <c r="A21" s="64" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
         </is>
       </c>
-      <c r="B21" s="65" t="inlineStr">
+      <c r="B21" s="64" t="inlineStr">
         <is>
           <t>Individuals who participate in advocacy or awareness campaigns on energy.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28.9" customHeight="1">
-      <c r="A22" s="65" t="inlineStr">
+      <c r="A22" s="64" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="B22" s="65" t="inlineStr">
+      <c r="B22" s="64" t="inlineStr">
         <is>
           <t>Policies, regulations, strategies, plans, or frameworks developed, approved, implemented, or strengthened.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="65" t="inlineStr">
+      <c r="A23" s="64" t="inlineStr">
         <is>
           <t>GHG Emissions Reduction</t>
         </is>
       </c>
-      <c r="B23" s="65" t="inlineStr">
+      <c r="B23" s="64" t="inlineStr">
         <is>
           <t>Greenhouse gas emissions reduced or mitigated, in tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="65" t="inlineStr">
+      <c r="A24" s="64" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="65" t="inlineStr">
+      <c r="B24" s="64" t="inlineStr">
         <is>
           <t>Energy-related output that does not fit the standard categories above.</t>
         </is>
